--- a/artfynd/A 53643-2025 artfynd.xlsx
+++ b/artfynd/A 53643-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119819842</v>
+        <v>119819840</v>
       </c>
       <c r="B2" t="n">
-        <v>91481</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>746471</v>
+        <v>746439</v>
       </c>
       <c r="R2" t="n">
-        <v>7293555</v>
+        <v>7293491</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -786,37 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119819845</v>
+        <v>119819848</v>
       </c>
       <c r="B3" t="n">
-        <v>91858</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -830,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>746444</v>
+        <v>746442</v>
       </c>
       <c r="R3" t="n">
-        <v>7293643</v>
+        <v>7293653</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119819843</v>
+        <v>119819834</v>
       </c>
       <c r="B4" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>746457</v>
+        <v>746530</v>
       </c>
       <c r="R4" t="n">
-        <v>7293627</v>
+        <v>7293711</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,12 +996,7 @@
         <v>119819841</v>
       </c>
       <c r="B5" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119819847</v>
+        <v>119819843</v>
       </c>
       <c r="B6" t="n">
-        <v>91852</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>746442</v>
+        <v>746457</v>
       </c>
       <c r="R6" t="n">
-        <v>7293646</v>
+        <v>7293627</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1230,37 +1205,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119819844</v>
+        <v>119819847</v>
       </c>
       <c r="B7" t="n">
-        <v>91870</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1274,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>746451</v>
+        <v>746442</v>
       </c>
       <c r="R7" t="n">
-        <v>7293635</v>
+        <v>7293646</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1338,6 +1308,324 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>119819845</v>
+      </c>
+      <c r="B8" t="n">
+        <v>93197</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vistbäcken, Nb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>746444</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7293643</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>119819844</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93209</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vistbäcken, Nb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>746451</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7293635</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>119819842</v>
+      </c>
+      <c r="B10" t="n">
+        <v>92841</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Vistbäcken, Nb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>746471</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7293555</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Älvsbyn</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Älvsby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 53643-2025 artfynd.xlsx
+++ b/artfynd/A 53643-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AZ10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819840</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819848</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819834</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819841</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819843</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819847</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,6 +1449,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819845</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1520,6 +1560,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819844</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1626,8 +1671,24 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119819842</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>